--- a/docs/v3/materialeliste.xlsx
+++ b/docs/v3/materialeliste.xlsx
@@ -5,22 +5,35 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\privat\rabbit-house\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\privat\rabbit-house\docs\v3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19FB3963-6E91-4013-9EBA-DA5A00A23BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE7020B-86F7-4424-AA12-C41146183872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12165" yWindow="1035" windowWidth="34095" windowHeight="18300" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
+    <workbookView xWindow="7230" yWindow="1185" windowWidth="34095" windowHeight="18300" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
   </bookViews>
   <sheets>
     <sheet name="materialeliste" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>Kategori</t>
   </si>
@@ -92,6 +105,21 @@
   </si>
   <si>
     <t>Prisoverslag</t>
+  </si>
+  <si>
+    <t>Konstruktion</t>
+  </si>
+  <si>
+    <t>Murpap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 cm * 20 meter </t>
+  </si>
+  <si>
+    <t>Bundrem</t>
+  </si>
+  <si>
+    <t>Toprem</t>
   </si>
 </sst>
 </file>
@@ -602,7 +630,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="6" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -623,6 +651,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="10" xfId="23" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20 % - Farve1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1207,20 +1238,41 @@
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="A8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2">
+        <v>99</v>
+      </c>
+      <c r="F8" s="2">
+        <f>C8*E8</f>
+        <v>99</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="A9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1231,8 +1283,12 @@
       <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
+      <c r="A10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -1243,6 +1299,9 @@
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
     </row>
@@ -1261,6 +1320,7 @@
     <hyperlink ref="G6" r:id="rId3" xr:uid="{ABFF7B92-54B5-4DD1-902D-CD3F20ADE0CF}"/>
     <hyperlink ref="G4" r:id="rId4" xr:uid="{8CCAF7E5-106F-47B8-9280-E8F7218A5778}"/>
     <hyperlink ref="G5" r:id="rId5" xr:uid="{B1653E0F-ACED-4CCF-A400-CFAAC3AE7DBB}"/>
+    <hyperlink ref="G8" r:id="rId6" xr:uid="{FAC46CC1-954E-4401-8371-771034A3763E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1506,20 +1566,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="38ca45d6-8f85-4c3a-993a-743aa40b1336" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="38ca45d6-8f85-4c3a-993a-743aa40b1336" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1542,14 +1602,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1551DD82-85F6-480E-8CF8-03738D4C4012}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E323FC16-0305-4970-AE77-B1379828493F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -1564,4 +1616,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1551DD82-85F6-480E-8CF8-03738D4C4012}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/docs/v3/materialeliste.xlsx
+++ b/docs/v3/materialeliste.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\privat\rabbit-house\docs\v3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE7020B-86F7-4424-AA12-C41146183872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71262DC9-FE49-4EC4-A841-C8D575B295C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7230" yWindow="1185" windowWidth="34095" windowHeight="18300" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
   </bookViews>
   <sheets>
     <sheet name="materialeliste" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
   <si>
     <t>Kategori</t>
   </si>
@@ -120,6 +120,21 @@
   </si>
   <si>
     <t>Toprem</t>
+  </si>
+  <si>
+    <t>Reglar</t>
+  </si>
+  <si>
+    <t>Reglar 45 x 95 x 3600 mm PT NTR-AB</t>
+  </si>
+  <si>
+    <t>Reglar 45 x 95 x 2400 mm PT NTR-AB</t>
+  </si>
+  <si>
+    <t>Reglar 47 x 100 x 3600 mm Gran C24</t>
+  </si>
+  <si>
+    <t>Reglar 47 x 100 x 2400 mm Gran C24</t>
   </si>
 </sst>
 </file>
@@ -1030,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B52E8CE-734F-4C5C-A774-DE01A3B04B39}">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="3" customWidth="1"/>
@@ -1164,8 +1179,13 @@
       <c r="H4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
+      <c r="L4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="6">
+        <f>SUM(F8:F12)</f>
+        <v>2395.1999999999998</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1250,10 +1270,10 @@
       <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="6">
         <v>99</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="6">
         <f>C8*E8</f>
         <v>99</v>
       </c>
@@ -1273,12 +1293,25 @@
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="6">
+        <v>71.099999999999994</v>
+      </c>
+      <c r="F9" s="6">
+        <f>C9*E9</f>
+        <v>142.19999999999999</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
     </row>
@@ -1287,14 +1320,27 @@
         <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="6">
+        <v>47.4</v>
+      </c>
+      <c r="F10" s="6">
+        <f>C10*E10</f>
+        <v>237</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
@@ -1302,16 +1348,67 @@
       <c r="A11" s="8" t="s">
         <v>24</v>
       </c>
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="6">
+        <v>63.9</v>
+      </c>
+      <c r="F11" s="6">
+        <f>C11*E11</f>
+        <v>127.8</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2">
+        <v>42</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="6">
+        <v>42.6</v>
+      </c>
+      <c r="F12" s="6">
+        <f>C12*E12</f>
+        <v>1789.2</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1321,6 +1418,10 @@
     <hyperlink ref="G4" r:id="rId4" xr:uid="{8CCAF7E5-106F-47B8-9280-E8F7218A5778}"/>
     <hyperlink ref="G5" r:id="rId5" xr:uid="{B1653E0F-ACED-4CCF-A400-CFAAC3AE7DBB}"/>
     <hyperlink ref="G8" r:id="rId6" xr:uid="{FAC46CC1-954E-4401-8371-771034A3763E}"/>
+    <hyperlink ref="G9" r:id="rId7" xr:uid="{C3AD733A-BB1C-4DD8-9997-7E1264E27325}"/>
+    <hyperlink ref="G10" r:id="rId8" xr:uid="{822C708A-89BB-4C41-85A2-7F46AE9C3AA4}"/>
+    <hyperlink ref="G11" r:id="rId9" xr:uid="{AB4A796C-54C2-42B8-BEA7-318533409B7B}"/>
+    <hyperlink ref="G12" r:id="rId10" xr:uid="{655A2597-DBF9-463B-8049-641996B3C27E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1566,20 +1667,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="38ca45d6-8f85-4c3a-993a-743aa40b1336" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="38ca45d6-8f85-4c3a-993a-743aa40b1336" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1602,6 +1703,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1551DD82-85F6-480E-8CF8-03738D4C4012}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E323FC16-0305-4970-AE77-B1379828493F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -1616,12 +1725,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1551DD82-85F6-480E-8CF8-03738D4C4012}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/docs/v3/materialeliste.xlsx
+++ b/docs/v3/materialeliste.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\privat\rabbit-house\docs\v3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71262DC9-FE49-4EC4-A841-C8D575B295C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAB072C-D5C6-495F-8E1B-DE391728D787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
+    <workbookView xWindow="15690" yWindow="630" windowWidth="34095" windowHeight="18300" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
   </bookViews>
   <sheets>
     <sheet name="materialeliste" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="35">
   <si>
     <t>Kategori</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>Reglar 47 x 100 x 2400 mm Gran C24</t>
+  </si>
+  <si>
+    <t>Tagkonstruktion</t>
   </si>
 </sst>
 </file>
@@ -645,7 +648,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="6" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -667,6 +670,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="10" xfId="23" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="10" xfId="27" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1045,10 +1051,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B52E8CE-734F-4C5C-A774-DE01A3B04B39}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -1403,12 +1409,160 @@
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1667,20 +1821,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="38ca45d6-8f85-4c3a-993a-743aa40b1336" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="38ca45d6-8f85-4c3a-993a-743aa40b1336" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1703,14 +1857,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1551DD82-85F6-480E-8CF8-03738D4C4012}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E323FC16-0305-4970-AE77-B1379828493F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -1725,4 +1871,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1551DD82-85F6-480E-8CF8-03738D4C4012}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/docs/v3/materialeliste.xlsx
+++ b/docs/v3/materialeliste.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\privat\rabbit-house\docs\v3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAB072C-D5C6-495F-8E1B-DE391728D787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BE053C-91E1-4C31-9967-1CFAB548DBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15690" yWindow="630" windowWidth="34095" windowHeight="18300" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
+    <workbookView xWindow="22245" yWindow="675" windowWidth="34095" windowHeight="18300" activeTab="1" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
   </bookViews>
   <sheets>
     <sheet name="materialeliste" sheetId="1" r:id="rId1"/>
+    <sheet name="tagkonstruktion_tagpap" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="76">
   <si>
     <t>Kategori</t>
   </si>
@@ -65,15 +66,9 @@
     <t>stk</t>
   </si>
   <si>
-    <t>Fundablok 50x20x15cm</t>
-  </si>
-  <si>
     <t>Cement 25 kg</t>
   </si>
   <si>
-    <t>Støbemix 0-16mm</t>
-  </si>
-  <si>
     <t>Leverandør</t>
   </si>
   <si>
@@ -138,6 +133,135 @@
   </si>
   <si>
     <t>Tagkonstruktion</t>
+  </si>
+  <si>
+    <t>Spær</t>
+  </si>
+  <si>
+    <t>Tagrende</t>
+  </si>
+  <si>
+    <t>Tagpap</t>
+  </si>
+  <si>
+    <t>OSB-plader</t>
+  </si>
+  <si>
+    <t>Beklædning</t>
+  </si>
+  <si>
+    <t>Voliernet</t>
+  </si>
+  <si>
+    <t>Klinkbeklædning</t>
+  </si>
+  <si>
+    <t>Vindpap</t>
+  </si>
+  <si>
+    <t>Klemmelister</t>
+  </si>
+  <si>
+    <t>Isolering</t>
+  </si>
+  <si>
+    <t>Spær 45x95x3000 mm Gran C24</t>
+  </si>
+  <si>
+    <t>18 mm 244x125cm</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Sternbræt</t>
+  </si>
+  <si>
+    <t>Støbemix 0-16 mm</t>
+  </si>
+  <si>
+    <t>Fundablok 50x20x15 cm</t>
+  </si>
+  <si>
+    <t>110 mm med nedløb 65 mm. Bag-eave (LAV side, hvor vandet løber).</t>
+  </si>
+  <si>
+    <t>Vinkelbeslag</t>
+  </si>
+  <si>
+    <t>Tagpap-søm + skruer + forbrugsstof</t>
+  </si>
+  <si>
+    <t>11*4 + 2*2</t>
+  </si>
+  <si>
+    <t>Gevindstang M10</t>
+  </si>
+  <si>
+    <t>Gevindstang M10 x 1000 mm</t>
+  </si>
+  <si>
+    <t>M10 møtrikker</t>
+  </si>
+  <si>
+    <t>pk.</t>
+  </si>
+  <si>
+    <t>NKT Fasteners møtrik M10 12 stk.</t>
+  </si>
+  <si>
+    <t>Tagfod</t>
+  </si>
+  <si>
+    <t>Vindskede</t>
+  </si>
+  <si>
+    <t>Tagfod sort aluminium 55 x 80 x 1000 mm</t>
+  </si>
+  <si>
+    <t>Vindskede sort aluminium 75 x 20 x 80 x 1000 mm</t>
+  </si>
+  <si>
+    <t>Murpap til Tagfod</t>
+  </si>
+  <si>
+    <t>Phønix murpap 15 cm x 20 meter</t>
+  </si>
+  <si>
+    <t>Alusøm 2,6 x 25 mm - 100 stk.</t>
+  </si>
+  <si>
+    <t>Træværk</t>
+  </si>
+  <si>
+    <t>21x120x3600 mm gran. Hele perimeter 19 m</t>
+  </si>
+  <si>
+    <t>Tagdækning</t>
+  </si>
+  <si>
+    <t>Phønix Selvbyggerpap 1×5 m</t>
+  </si>
+  <si>
+    <t>Klæbeasfalt</t>
+  </si>
+  <si>
+    <t>Phønix klæbeasfalt 310 ml</t>
+  </si>
+  <si>
+    <t>Aluinddækning</t>
+  </si>
+  <si>
+    <t>Vandhåndtering</t>
+  </si>
+  <si>
+    <t>110 mm</t>
+  </si>
+  <si>
+    <t>Reglar 45x95x3000 mm Gran C24</t>
+  </si>
+  <si>
+    <t>OSB-3 plade TG4 18 mm - 2397 x 600 mm</t>
   </si>
 </sst>
 </file>
@@ -648,7 +772,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="6" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -673,6 +797,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="10" xfId="27" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="10" xfId="35" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1051,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B52E8CE-734F-4C5C-A774-DE01A3B04B39}">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -1088,7 +1227,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -1105,7 +1244,7 @@
         <v>1050</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2" s="6">
         <v>0.55000000000000004</v>
@@ -1115,13 +1254,13 @@
         <v>577.5</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M2"/>
     </row>
@@ -1130,7 +1269,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2">
         <v>120</v>
@@ -1146,17 +1285,17 @@
         <v>1890</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M3" s="6">
-        <f>SUM(F2:F6)</f>
-        <v>4884.3500000000004</v>
+        <f>SUM(F2:F8)</f>
+        <v>5445.35</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -1164,7 +1303,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2">
         <v>13</v>
@@ -1180,17 +1319,17 @@
         <v>386.75</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M4" s="6">
-        <f>SUM(F8:F12)</f>
-        <v>2395.1999999999998</v>
+        <f>SUM(F10:F14)</f>
+        <v>2523</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -1198,7 +1337,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2">
         <v>14</v>
@@ -1214,12 +1353,14 @@
         <v>1050</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>32</v>
+      </c>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -1227,13 +1368,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2">
         <v>1485</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6" s="6">
         <v>0.66</v>
@@ -1243,119 +1384,119 @@
         <v>980.1</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="A7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="2">
+        <v>18</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="6">
+        <v>27.95</v>
+      </c>
+      <c r="F7" s="6">
+        <f>C7*E7</f>
+        <v>503.09999999999997</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>24</v>
+      <c r="A8" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="E8" s="6">
-        <v>99</v>
+        <v>28.95</v>
       </c>
       <c r="F8" s="6">
         <f>C8*E8</f>
-        <v>99</v>
+        <v>57.9</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="6">
-        <v>71.099999999999994</v>
-      </c>
-      <c r="F9" s="6">
-        <f>C9*E9</f>
-        <v>142.19999999999999</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>30</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="6">
-        <v>47.4</v>
+        <v>99</v>
       </c>
       <c r="F10" s="6">
         <f>C10*E10</f>
-        <v>237</v>
+        <v>99</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2">
         <v>2</v>
@@ -1364,73 +1505,105 @@
         <v>9</v>
       </c>
       <c r="E11" s="6">
-        <v>63.9</v>
+        <v>71.099999999999994</v>
       </c>
       <c r="F11" s="6">
         <f>C11*E11</f>
-        <v>127.8</v>
+        <v>142.19999999999999</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="6">
-        <v>42.6</v>
+        <v>47.4</v>
       </c>
       <c r="F12" s="6">
         <f>C12*E12</f>
-        <v>1789.2</v>
+        <v>237</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="A13" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="2">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="6">
+        <v>63.9</v>
+      </c>
+      <c r="F13" s="6">
+        <f>C13*E13</f>
+        <v>255.6</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="A14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="2">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="6">
+        <v>42.6</v>
+      </c>
+      <c r="F14" s="6">
+        <f>C14*E14</f>
+        <v>1789.2</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
     </row>
@@ -1443,6 +1616,8 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -1453,46 +1628,842 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="6">
+        <v>53.25</v>
+      </c>
+      <c r="F18" s="6">
+        <f>C18*E18</f>
+        <v>692.25</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="2">
+        <v>7</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="2">
+        <v>6</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="6">
+        <v>92.7</v>
+      </c>
+      <c r="F20" s="6">
+        <f>C20*E20</f>
+        <v>556.20000000000005</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="2">
+        <v>5</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="2">
+        <v>7</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="6">
+        <v>39.75</v>
+      </c>
+      <c r="F24" s="6">
+        <f>C24*E24</f>
+        <v>278.25</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="6">
+        <v>149</v>
+      </c>
+      <c r="F25" s="6">
+        <f>C25*E25</f>
+        <v>149</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="2">
+        <v>13</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="6">
+        <v>42.75</v>
+      </c>
+      <c r="F26" s="6">
+        <f>C26*E26</f>
+        <v>555.75</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="2">
+        <v>48</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="6">
+        <v>69.95</v>
+      </c>
+      <c r="F29" s="6">
+        <f>C29*E29</f>
+        <v>69.95</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{F4F18C84-7C2A-48FB-8004-317535792BC3}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{ADFA0A0F-4714-409E-8183-2D1DC6F6AF6F}"/>
+    <hyperlink ref="G6" r:id="rId3" xr:uid="{ABFF7B92-54B5-4DD1-902D-CD3F20ADE0CF}"/>
+    <hyperlink ref="G4" r:id="rId4" xr:uid="{8CCAF7E5-106F-47B8-9280-E8F7218A5778}"/>
+    <hyperlink ref="G5" r:id="rId5" xr:uid="{B1653E0F-ACED-4CCF-A400-CFAAC3AE7DBB}"/>
+    <hyperlink ref="G10" r:id="rId6" xr:uid="{FAC46CC1-954E-4401-8371-771034A3763E}"/>
+    <hyperlink ref="G11" r:id="rId7" xr:uid="{C3AD733A-BB1C-4DD8-9997-7E1264E27325}"/>
+    <hyperlink ref="G12" r:id="rId8" xr:uid="{822C708A-89BB-4C41-85A2-7F46AE9C3AA4}"/>
+    <hyperlink ref="G13" r:id="rId9" xr:uid="{AB4A796C-54C2-42B8-BEA7-318533409B7B}"/>
+    <hyperlink ref="G14" r:id="rId10" xr:uid="{655A2597-DBF9-463B-8049-641996B3C27E}"/>
+    <hyperlink ref="G7" r:id="rId11" xr:uid="{FD55BB59-34E1-441E-8248-D0E1715D035D}"/>
+    <hyperlink ref="G8" r:id="rId12" xr:uid="{BD300C6F-9638-4146-BB8B-372C01FFC096}"/>
+    <hyperlink ref="G24" r:id="rId13" xr:uid="{E21D12DD-F505-4866-BB7C-6A9951005D0A}"/>
+    <hyperlink ref="G26" r:id="rId14" xr:uid="{814FA9A0-8484-4BA4-B9BC-F75552780775}"/>
+    <hyperlink ref="G25" r:id="rId15" xr:uid="{1108F905-647A-4724-8D26-8FC9DC9A6CDC}"/>
+    <hyperlink ref="G29" r:id="rId16" xr:uid="{F3D1896A-0A8E-4431-804E-4BFE3A5D1E0F}"/>
+    <hyperlink ref="G18" r:id="rId17" xr:uid="{667E39DA-69FB-4FDB-AE56-9199355A0E59}"/>
+    <hyperlink ref="G20" r:id="rId18" xr:uid="{D995632A-8B73-4B02-BC8C-B33176F50528}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0D1006-3169-40A0-B66F-4490656895FA}">
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="68" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="9.140625" style="3"/>
+    <col min="12" max="12" width="17" style="3" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="6">
+        <v>53.25</v>
+      </c>
+      <c r="F5" s="6">
+        <f>C5*E5</f>
+        <v>692.25</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="2">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="6">
+        <v>129</v>
+      </c>
+      <c r="F6" s="6">
+        <f>C6*E6</f>
+        <v>1935</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="2">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="6">
+        <v>92.7</v>
+      </c>
+      <c r="F7" s="6">
+        <f>C7*E7</f>
+        <v>556.20000000000005</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="6">
+        <v>579</v>
+      </c>
+      <c r="F10" s="6">
+        <f>C10*E10</f>
+        <v>2895</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="6">
+        <v>69.95</v>
+      </c>
+      <c r="F11" s="6">
+        <f>C11*E11</f>
+        <v>209.85000000000002</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="6">
+        <v>149</v>
+      </c>
+      <c r="F12" s="6">
+        <f>C12*E12</f>
+        <v>149</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="2">
+        <v>7</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="6">
+        <v>39.75</v>
+      </c>
+      <c r="F15" s="6">
+        <f>C15*E15</f>
+        <v>278.25</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="2">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="6">
+        <v>42.75</v>
+      </c>
+      <c r="F16" s="6">
+        <f>C16*E16</f>
+        <v>555.75</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
+      <c r="A17"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="5"/>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="A18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>72</v>
+      </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="5"/>
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="A19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
+      <c r="H19" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="A20" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="6">
+        <v>69.95</v>
+      </c>
+      <c r="F20" s="6">
+        <f>C20*E20</f>
+        <v>69.95</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
@@ -1524,58 +2495,37 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="2">
+        <v>48</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{F4F18C84-7C2A-48FB-8004-317535792BC3}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{ADFA0A0F-4714-409E-8183-2D1DC6F6AF6F}"/>
-    <hyperlink ref="G6" r:id="rId3" xr:uid="{ABFF7B92-54B5-4DD1-902D-CD3F20ADE0CF}"/>
-    <hyperlink ref="G4" r:id="rId4" xr:uid="{8CCAF7E5-106F-47B8-9280-E8F7218A5778}"/>
-    <hyperlink ref="G5" r:id="rId5" xr:uid="{B1653E0F-ACED-4CCF-A400-CFAAC3AE7DBB}"/>
-    <hyperlink ref="G8" r:id="rId6" xr:uid="{FAC46CC1-954E-4401-8371-771034A3763E}"/>
-    <hyperlink ref="G9" r:id="rId7" xr:uid="{C3AD733A-BB1C-4DD8-9997-7E1264E27325}"/>
-    <hyperlink ref="G10" r:id="rId8" xr:uid="{822C708A-89BB-4C41-85A2-7F46AE9C3AA4}"/>
-    <hyperlink ref="G11" r:id="rId9" xr:uid="{AB4A796C-54C2-42B8-BEA7-318533409B7B}"/>
-    <hyperlink ref="G12" r:id="rId10" xr:uid="{655A2597-DBF9-463B-8049-641996B3C27E}"/>
+    <hyperlink ref="G16" r:id="rId1" xr:uid="{DCF914A9-39ED-487F-9A1A-C7568C7045D0}"/>
+    <hyperlink ref="G20" r:id="rId2" xr:uid="{3F18322E-CE0D-43AB-B231-92958E9070D0}"/>
+    <hyperlink ref="G5" r:id="rId3" xr:uid="{39831712-2ECB-4199-B56F-E4840BACF375}"/>
+    <hyperlink ref="G7" r:id="rId4" xr:uid="{39F52C62-2C65-4769-ABCB-A5176588F8B5}"/>
+    <hyperlink ref="G10" r:id="rId5" xr:uid="{B7063941-72D2-4AFC-B2C5-36EDBB67635E}"/>
+    <hyperlink ref="G11" r:id="rId6" xr:uid="{F1AA7713-8D33-45BD-AD42-645F4CAC3A5B}"/>
+    <hyperlink ref="G15" r:id="rId7" xr:uid="{CD9130B6-3E34-4D80-882D-0B5C95174CB6}"/>
+    <hyperlink ref="G12" r:id="rId8" xr:uid="{8AA49080-3CA7-4021-BA9A-A13183FEE9D8}"/>
+    <hyperlink ref="G6" r:id="rId9" xr:uid="{A59266F8-9FD2-46DC-A80A-B093D8DF714C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/v3/materialeliste.xlsx
+++ b/docs/v3/materialeliste.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\privat\rabbit-house\docs\v3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BE053C-91E1-4C31-9967-1CFAB548DBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB13144-7F09-4ECA-9FF3-DA49822E7600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22245" yWindow="675" windowWidth="34095" windowHeight="18300" activeTab="1" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
+    <workbookView xWindow="15660" yWindow="675" windowWidth="34095" windowHeight="18300" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
   </bookViews>
   <sheets>
     <sheet name="materialeliste" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="90">
   <si>
     <t>Kategori</t>
   </si>
@@ -165,12 +165,6 @@
     <t>Isolering</t>
   </si>
   <si>
-    <t>Spær 45x95x3000 mm Gran C24</t>
-  </si>
-  <si>
-    <t>18 mm 244x125cm</t>
-  </si>
-  <si>
     <t>m</t>
   </si>
   <si>
@@ -183,15 +177,9 @@
     <t>Fundablok 50x20x15 cm</t>
   </si>
   <si>
-    <t>110 mm med nedløb 65 mm. Bag-eave (LAV side, hvor vandet løber).</t>
-  </si>
-  <si>
     <t>Vinkelbeslag</t>
   </si>
   <si>
-    <t>Tagpap-søm + skruer + forbrugsstof</t>
-  </si>
-  <si>
     <t>11*4 + 2*2</t>
   </si>
   <si>
@@ -213,15 +201,9 @@
     <t>Tagfod</t>
   </si>
   <si>
-    <t>Vindskede</t>
-  </si>
-  <si>
     <t>Tagfod sort aluminium 55 x 80 x 1000 mm</t>
   </si>
   <si>
-    <t>Vindskede sort aluminium 75 x 20 x 80 x 1000 mm</t>
-  </si>
-  <si>
     <t>Murpap til Tagfod</t>
   </si>
   <si>
@@ -255,13 +237,73 @@
     <t>Vandhåndtering</t>
   </si>
   <si>
-    <t>110 mm</t>
-  </si>
-  <si>
     <t>Reglar 45x95x3000 mm Gran C24</t>
   </si>
   <si>
     <t>OSB-3 plade TG4 18 mm - 2397 x 600 mm</t>
+  </si>
+  <si>
+    <t>Sternkapsel</t>
+  </si>
+  <si>
+    <t>Sternkapsel lige sort 35 x 25 mm x 100 cm</t>
+  </si>
+  <si>
+    <t>Tagrende-beslag</t>
+  </si>
+  <si>
+    <t>Endebund tagrende 110 mm</t>
+  </si>
+  <si>
+    <t>Bladsamler</t>
+  </si>
+  <si>
+    <t>Nedløbsrør</t>
+  </si>
+  <si>
+    <t>Nedløbsbøjning</t>
+  </si>
+  <si>
+    <t>Beslag og fastgørelse</t>
+  </si>
+  <si>
+    <t>OSB/spær-skruer 5x80mm</t>
+  </si>
+  <si>
+    <t>Rustfri tagskruer m. EPDM-pakning</t>
+  </si>
+  <si>
+    <t>Galvaniseret tagpapsøm</t>
+  </si>
+  <si>
+    <t>Ø75 mm x 3 m. Fra tagrende ned til faldsten. Stål</t>
+  </si>
+  <si>
+    <t>Anvendes til at dreje nedløbsrøret ind til væggen. Vinkel: 70 gr.</t>
+  </si>
+  <si>
+    <t>4+3 meter</t>
+  </si>
+  <si>
+    <t>Samlestykke</t>
+  </si>
+  <si>
+    <t>Endebund til at lukke Rodena tagrender af i både højre og venstre side. Lavet af stål i farven silver metallic</t>
+  </si>
+  <si>
+    <t>Anvendes til at samle to tagrender i længderetningen. Stål</t>
+  </si>
+  <si>
+    <t>Konsoljern stål, 90 grader. Anvendes til at holde tagrenden.</t>
+  </si>
+  <si>
+    <t>Anvendes til at sætte i tudstykket for at forhindre at blade og små kviste skal glide ned i nedløbsrøret</t>
+  </si>
+  <si>
+    <t>Tudstykke</t>
+  </si>
+  <si>
+    <t>Anvendes til at koble nedløbsrøret til tagrenden. Ø75 mm. Silver metallic stål</t>
   </si>
 </sst>
 </file>
@@ -772,7 +814,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="6" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -814,6 +856,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20 % - Farve1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1190,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B52E8CE-734F-4C5C-A774-DE01A3B04B39}">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -1200,7 +1243,7 @@
     <col min="5" max="5" width="22" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="68" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="95.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="9.140625" style="3"/>
     <col min="12" max="12" width="17" style="3" customWidth="1"/>
     <col min="13" max="13" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -1269,7 +1312,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C3" s="2">
         <v>120</v>
@@ -1361,14 +1404,17 @@
       <c r="L5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="2"/>
+      <c r="M5" s="6">
+        <f>SUM(F17:F45)</f>
+        <v>8711.9500000000007</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" s="2">
         <v>1485</v>
@@ -1397,7 +1443,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C7" s="2">
         <v>18</v>
@@ -1416,7 +1462,7 @@
         <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -1426,13 +1472,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E8" s="6">
         <v>28.95</v>
@@ -1445,7 +1491,7 @@
         <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -1636,7 +1682,7 @@
         <v>32</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -1671,7 +1717,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1684,16 +1730,23 @@
         <v>36</v>
       </c>
       <c r="C19" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="2"/>
+      <c r="E19" s="6">
+        <v>129</v>
+      </c>
+      <c r="F19" s="6">
+        <f>C19*E19</f>
+        <v>1935</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="H19" s="2" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
@@ -1703,7 +1756,7 @@
         <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2">
         <v>6</v>
@@ -1722,11 +1775,11 @@
         <v>16</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -1742,7 +1795,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -1766,11 +1819,18 @@
       <c r="D23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="2"/>
+      <c r="E23" s="6">
+        <v>579</v>
+      </c>
+      <c r="F23" s="6">
+        <f>C23*E23</f>
+        <v>2895</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="H23" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -1778,26 +1838,26 @@
         <v>32</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C24" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="6">
-        <v>39.75</v>
+        <v>69.95</v>
       </c>
       <c r="F24" s="6">
         <f>C24*E24</f>
-        <v>278.25</v>
+        <v>209.85000000000002</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -1805,7 +1865,7 @@
         <v>32</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -1824,74 +1884,58 @@
         <v>16</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="2">
-        <v>13</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="F26" s="6">
-        <f>C26*E26</f>
-        <v>555.75</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>61</v>
-      </c>
+      <c r="A26" s="15"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="B27" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="2"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C28" s="2">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="2"/>
+      <c r="E28" s="6">
+        <v>39.75</v>
+      </c>
+      <c r="F28" s="6">
+        <f>C28*E28</f>
+        <v>278.25</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="H28" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -1899,115 +1943,428 @@
         <v>32</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C29" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="E29" s="6">
-        <v>69.95</v>
+        <v>59.95</v>
       </c>
       <c r="F29" s="6">
         <f>C29*E29</f>
-        <v>69.95</v>
+        <v>779.35</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="5"/>
       <c r="H30" s="2"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
+      <c r="A31" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>66</v>
+      </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="5"/>
       <c r="H31" s="2"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
+      <c r="A32" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="2">
+        <v>7</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="6">
+        <v>49.95</v>
+      </c>
+      <c r="F32" s="6">
+        <f>C32*E32</f>
+        <v>349.65000000000003</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="2">
+        <v>10</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="6">
+        <v>24.95</v>
+      </c>
+      <c r="F33" s="6">
+        <f>C33*E33</f>
+        <v>249.5</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="6">
+        <v>46.75</v>
+      </c>
+      <c r="F34" s="6">
+        <f>E34*C34</f>
+        <v>46.75</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" s="2">
+        <v>2</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="6">
+        <v>43.75</v>
+      </c>
+      <c r="F35" s="6">
+        <f>C35*E35</f>
+        <v>87.5</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="6">
+        <v>19.95</v>
+      </c>
+      <c r="F36" s="6">
+        <f>C36*E36</f>
+        <v>19.95</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="6">
+        <v>210</v>
+      </c>
+      <c r="F37" s="6">
+        <f>C37*E37</f>
+        <v>210</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="6">
+        <v>78.75</v>
+      </c>
+      <c r="F38" s="6">
+        <f>C38*E38</f>
+        <v>78.75</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="6">
+        <v>105</v>
+      </c>
+      <c r="F39" s="6">
+        <f>C39*E39</f>
+        <v>105</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="2">
+        <v>48</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" s="2">
+        <v>250</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="6">
+        <v>69.95</v>
+      </c>
+      <c r="F45" s="6">
+        <f>C45*E45</f>
+        <v>69.95</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B48" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B49" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B51" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B52" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2025,21 +2382,32 @@
     <hyperlink ref="G14" r:id="rId10" xr:uid="{655A2597-DBF9-463B-8049-641996B3C27E}"/>
     <hyperlink ref="G7" r:id="rId11" xr:uid="{FD55BB59-34E1-441E-8248-D0E1715D035D}"/>
     <hyperlink ref="G8" r:id="rId12" xr:uid="{BD300C6F-9638-4146-BB8B-372C01FFC096}"/>
-    <hyperlink ref="G24" r:id="rId13" xr:uid="{E21D12DD-F505-4866-BB7C-6A9951005D0A}"/>
-    <hyperlink ref="G26" r:id="rId14" xr:uid="{814FA9A0-8484-4BA4-B9BC-F75552780775}"/>
-    <hyperlink ref="G25" r:id="rId15" xr:uid="{1108F905-647A-4724-8D26-8FC9DC9A6CDC}"/>
-    <hyperlink ref="G29" r:id="rId16" xr:uid="{F3D1896A-0A8E-4431-804E-4BFE3A5D1E0F}"/>
-    <hyperlink ref="G18" r:id="rId17" xr:uid="{667E39DA-69FB-4FDB-AE56-9199355A0E59}"/>
-    <hyperlink ref="G20" r:id="rId18" xr:uid="{D995632A-8B73-4B02-BC8C-B33176F50528}"/>
+    <hyperlink ref="G18" r:id="rId13" xr:uid="{98902821-B69F-412E-AA6C-49250E0607BB}"/>
+    <hyperlink ref="G20" r:id="rId14" xr:uid="{A3BA01B0-716E-4A8A-B261-0277253862F9}"/>
+    <hyperlink ref="G23" r:id="rId15" xr:uid="{61B7C4B2-5E9D-453F-AF0E-2B11632D1523}"/>
+    <hyperlink ref="G24" r:id="rId16" xr:uid="{1556E857-5EA4-4AFD-A46D-DA68FCE0C368}"/>
+    <hyperlink ref="G28" r:id="rId17" xr:uid="{2A1B6AD6-9195-4308-96DA-B367781D8834}"/>
+    <hyperlink ref="G25" r:id="rId18" xr:uid="{D47075DF-0C65-4328-8143-AC391C5CB0E1}"/>
+    <hyperlink ref="G19" r:id="rId19" xr:uid="{4FDD94E9-90D8-43F2-907C-946B9881176C}"/>
+    <hyperlink ref="G29" r:id="rId20" xr:uid="{CC2F3AA5-2390-4502-B846-73502945F531}"/>
+    <hyperlink ref="G45" r:id="rId21" xr:uid="{BDABF779-BB8F-4FB8-B47F-5564583B87F7}"/>
+    <hyperlink ref="G37" r:id="rId22" xr:uid="{CEF38967-2469-4D49-A02D-F472126F1E40}"/>
+    <hyperlink ref="G38" r:id="rId23" xr:uid="{B2CE4942-5540-41C3-BA97-6490679B9538}"/>
+    <hyperlink ref="G32" r:id="rId24" xr:uid="{ACBF5DF3-DCAE-4B46-ADBF-4ED14628DEAD}"/>
+    <hyperlink ref="G34" r:id="rId25" xr:uid="{3C7A8F56-ABC4-48F1-81CB-AA4666067E19}"/>
+    <hyperlink ref="G35" r:id="rId26" xr:uid="{BB3E73A9-E185-45C0-B602-B5CA391A8E3D}"/>
+    <hyperlink ref="G33" r:id="rId27" xr:uid="{6E92EC5D-CAC7-440C-BF15-9DA01ECB766F}"/>
+    <hyperlink ref="G36" r:id="rId28" xr:uid="{8249F3D4-5A22-4913-B3CE-0088DB84F686}"/>
+    <hyperlink ref="G39" r:id="rId29" xr:uid="{18655CD5-F404-4A1C-BCC9-5252BAFDF36C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId30"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0D1006-3169-40A0-B66F-4490656895FA}">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -2049,14 +2417,14 @@
     <col min="5" max="5" width="22" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="68" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="95.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="9.140625" style="3"/>
     <col min="12" max="12" width="17" style="3" customWidth="1"/>
     <col min="13" max="13" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2082,7 +2450,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2091,10 +2459,12 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2103,15 +2473,17 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2119,10 +2491,12 @@
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
       <c r="H4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>32</v>
       </c>
@@ -2146,12 +2520,14 @@
         <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>32</v>
       </c>
@@ -2175,17 +2551,17 @@
         <v>16</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2">
         <v>6</v>
@@ -2204,11 +2580,11 @@
         <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -2219,12 +2595,12 @@
       <c r="L8" s="11"/>
       <c r="M8" s="11"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -2235,7 +2611,7 @@
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>32</v>
       </c>
@@ -2259,15 +2635,15 @@
         <v>16</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C11" s="2">
         <v>3</v>
@@ -2286,15 +2662,15 @@
         <v>16</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -2313,11 +2689,11 @@
         <v>16</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -2326,12 +2702,12 @@
       <c r="G13" s="5"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -2340,12 +2716,12 @@
       <c r="G14" s="5"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C15" s="2">
         <v>7</v>
@@ -2364,15 +2740,15 @@
         <v>16</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C16" s="2">
         <v>13</v>
@@ -2381,21 +2757,21 @@
         <v>9</v>
       </c>
       <c r="E16" s="6">
-        <v>42.75</v>
+        <v>59.95</v>
       </c>
       <c r="F16" s="6">
         <f>C16*E16</f>
-        <v>555.75</v>
+        <v>779.35</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -2409,7 +2785,7 @@
         <v>32</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -2426,16 +2802,23 @@
         <v>34</v>
       </c>
       <c r="C19" s="2">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="E19" s="6">
+        <v>49.95</v>
+      </c>
+      <c r="F19" s="6">
+        <f>C19*E19</f>
+        <v>349.65000000000003</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="H19" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -2443,89 +2826,312 @@
         <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C20" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="E20" s="6">
-        <v>69.95</v>
+        <v>24.95</v>
       </c>
       <c r="F20" s="6">
         <f>C20*E20</f>
-        <v>69.95</v>
+        <v>249.5</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
+      <c r="A21" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="6">
+        <v>46.75</v>
+      </c>
+      <c r="F21" s="6">
+        <f>E21*C21</f>
+        <v>46.75</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
+      <c r="A22" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="6">
+        <v>43.75</v>
+      </c>
+      <c r="F22" s="6">
+        <f>C22*E22</f>
+        <v>87.5</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
+      <c r="A23" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="6">
+        <v>19.95</v>
+      </c>
+      <c r="F23" s="6">
+        <f>C23*E23</f>
+        <v>19.95</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="6">
+        <v>210</v>
+      </c>
+      <c r="F24" s="6">
+        <f>C24*E24</f>
+        <v>210</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="6">
+        <v>78.75</v>
+      </c>
+      <c r="F25" s="6">
+        <f>C25*E25</f>
+        <v>78.75</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="6">
+        <v>105</v>
+      </c>
+      <c r="F26" s="6">
+        <f>C26*E26</f>
+        <v>105</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="2">
+      <c r="B28" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="2">
         <v>48</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="2">
+        <v>250</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>52</v>
+      </c>
+      <c r="E32" s="6">
+        <v>69.95</v>
+      </c>
+      <c r="F32" s="6">
+        <f>C32*E32</f>
+        <v>69.95</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G16" r:id="rId1" xr:uid="{DCF914A9-39ED-487F-9A1A-C7568C7045D0}"/>
-    <hyperlink ref="G20" r:id="rId2" xr:uid="{3F18322E-CE0D-43AB-B231-92958E9070D0}"/>
-    <hyperlink ref="G5" r:id="rId3" xr:uid="{39831712-2ECB-4199-B56F-E4840BACF375}"/>
-    <hyperlink ref="G7" r:id="rId4" xr:uid="{39F52C62-2C65-4769-ABCB-A5176588F8B5}"/>
-    <hyperlink ref="G10" r:id="rId5" xr:uid="{B7063941-72D2-4AFC-B2C5-36EDBB67635E}"/>
-    <hyperlink ref="G11" r:id="rId6" xr:uid="{F1AA7713-8D33-45BD-AD42-645F4CAC3A5B}"/>
-    <hyperlink ref="G15" r:id="rId7" xr:uid="{CD9130B6-3E34-4D80-882D-0B5C95174CB6}"/>
-    <hyperlink ref="G12" r:id="rId8" xr:uid="{8AA49080-3CA7-4021-BA9A-A13183FEE9D8}"/>
-    <hyperlink ref="G6" r:id="rId9" xr:uid="{A59266F8-9FD2-46DC-A80A-B093D8DF714C}"/>
+    <hyperlink ref="G5" r:id="rId1" xr:uid="{39831712-2ECB-4199-B56F-E4840BACF375}"/>
+    <hyperlink ref="G7" r:id="rId2" xr:uid="{39F52C62-2C65-4769-ABCB-A5176588F8B5}"/>
+    <hyperlink ref="G10" r:id="rId3" xr:uid="{B7063941-72D2-4AFC-B2C5-36EDBB67635E}"/>
+    <hyperlink ref="G11" r:id="rId4" xr:uid="{F1AA7713-8D33-45BD-AD42-645F4CAC3A5B}"/>
+    <hyperlink ref="G15" r:id="rId5" xr:uid="{CD9130B6-3E34-4D80-882D-0B5C95174CB6}"/>
+    <hyperlink ref="G12" r:id="rId6" xr:uid="{8AA49080-3CA7-4021-BA9A-A13183FEE9D8}"/>
+    <hyperlink ref="G6" r:id="rId7" xr:uid="{A59266F8-9FD2-46DC-A80A-B093D8DF714C}"/>
+    <hyperlink ref="G16" r:id="rId8" xr:uid="{FD956658-A542-4C7B-9247-FEDD0600982D}"/>
+    <hyperlink ref="G32" r:id="rId9" xr:uid="{36F362C3-EF62-4DD6-BE43-B25596AFD49D}"/>
+    <hyperlink ref="G24" r:id="rId10" xr:uid="{49EF6539-39C5-4F79-AA54-440607D617FE}"/>
+    <hyperlink ref="G25" r:id="rId11" xr:uid="{4D4A6454-D114-42B1-BDF5-48F04A245EA8}"/>
+    <hyperlink ref="G19" r:id="rId12" xr:uid="{990937CE-28ED-4C96-A19E-68EF37542702}"/>
+    <hyperlink ref="G21" r:id="rId13" xr:uid="{667FF7B8-D109-4359-B819-1FA412745D28}"/>
+    <hyperlink ref="G22" r:id="rId14" xr:uid="{E233421D-6024-4AE5-B4E4-531F3F514A1C}"/>
+    <hyperlink ref="G20" r:id="rId15" xr:uid="{4E0790A3-740A-4351-AD65-9371A6522635}"/>
+    <hyperlink ref="G23" r:id="rId16" xr:uid="{753B3D2B-9425-4778-B826-64FAF8AD812B}"/>
+    <hyperlink ref="G26" r:id="rId17" xr:uid="{22B2D0EF-5DC6-4957-8EEC-2CE4DB06698E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/v3/materialeliste.xlsx
+++ b/docs/v3/materialeliste.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\privat\rabbit-house\docs\v3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB13144-7F09-4ECA-9FF3-DA49822E7600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742AF6E6-A45B-4CBE-BC3D-46955AB120BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15660" yWindow="675" windowWidth="34095" windowHeight="18300" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
+    <workbookView xWindow="15660" yWindow="0" windowWidth="33960" windowHeight="20985" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
   </bookViews>
   <sheets>
     <sheet name="materialeliste" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="101">
   <si>
     <t>Kategori</t>
   </si>
@@ -304,6 +304,39 @@
   </si>
   <si>
     <t>Anvendes til at koble nedløbsrøret til tagrenden. Ø75 mm. Silver metallic stål</t>
+  </si>
+  <si>
+    <t>1x 10 meter og 1x 25 meter</t>
+  </si>
+  <si>
+    <t>Klamper til Voliernet</t>
+  </si>
+  <si>
+    <t>Hjørnetrim</t>
+  </si>
+  <si>
+    <t>45x45 mm x 2400 mm</t>
+  </si>
+  <si>
+    <t>Sortmalet klinkbeklædning lavet af gran. Mål: 25 x 125 mm - høvlet mål: 9/22 x 105 mm og med en længde på 4,2 meter. Pakke á 6 stk.</t>
+  </si>
+  <si>
+    <t>m2</t>
+  </si>
+  <si>
+    <t>2 vægge á ~6m2. 2 vægge á ~4m2.</t>
+  </si>
+  <si>
+    <t>rl.</t>
+  </si>
+  <si>
+    <t>17,5 m^2 behov. 20 m2 pr. rulle.</t>
+  </si>
+  <si>
+    <t>25x50 mm x 4200 mm</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -814,7 +847,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="6" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -844,19 +877,16 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="10" xfId="35" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20 % - Farve1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1233,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B52E8CE-734F-4C5C-A774-DE01A3B04B39}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -1243,10 +1273,10 @@
     <col min="5" max="5" width="22" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="95.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="119.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="9.140625" style="3"/>
     <col min="12" max="12" width="17" style="3" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
@@ -1293,7 +1323,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F2" s="6">
-        <f>C2*E2</f>
+        <f t="shared" ref="F2:F8" si="0">C2*E2</f>
         <v>577.5</v>
       </c>
       <c r="G2" s="5" t="s">
@@ -1324,7 +1354,7 @@
         <v>15.75</v>
       </c>
       <c r="F3" s="6">
-        <f>C3*E3</f>
+        <f t="shared" si="0"/>
         <v>1890</v>
       </c>
       <c r="G3" s="5" t="s">
@@ -1358,7 +1388,7 @@
         <v>29.75</v>
       </c>
       <c r="F4" s="6">
-        <f>C4*E4</f>
+        <f t="shared" si="0"/>
         <v>386.75</v>
       </c>
       <c r="G4" s="5" t="s">
@@ -1392,7 +1422,7 @@
         <v>75</v>
       </c>
       <c r="F5" s="6">
-        <f>C5*E5</f>
+        <f t="shared" si="0"/>
         <v>1050</v>
       </c>
       <c r="G5" s="5" t="s">
@@ -1426,7 +1456,7 @@
         <v>0.66</v>
       </c>
       <c r="F6" s="6">
-        <f>C6*E6</f>
+        <f t="shared" si="0"/>
         <v>980.1</v>
       </c>
       <c r="G6" s="5" t="s">
@@ -1435,11 +1465,16 @@
       <c r="H6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
+      <c r="L6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" s="6">
+        <f>SUM(F48:F54)</f>
+        <v>5627.9</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1455,7 +1490,7 @@
         <v>27.95</v>
       </c>
       <c r="F7" s="6">
-        <f>C7*E7</f>
+        <f t="shared" si="0"/>
         <v>503.09999999999997</v>
       </c>
       <c r="G7" s="5" t="s">
@@ -1468,7 +1503,7 @@
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1484,7 +1519,7 @@
         <v>28.95</v>
       </c>
       <c r="F8" s="6">
-        <f>C8*E8</f>
+        <f t="shared" si="0"/>
         <v>57.9</v>
       </c>
       <c r="G8" s="5" t="s">
@@ -1592,8 +1627,13 @@
       <c r="H12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+      <c r="L12" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="M12" s="14">
+        <f>SUM(M3:M11)</f>
+        <v>22308.200000000004</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
@@ -1681,7 +1721,7 @@
       <c r="A17" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="2"/>
@@ -1748,8 +1788,6 @@
       <c r="H19" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
@@ -1779,7 +1817,7 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="13"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -1787,14 +1825,12 @@
       <c r="F21" s="6"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C22" s="2"/>
@@ -1803,8 +1839,6 @@
       <c r="F22" s="6"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
@@ -1888,7 +1922,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
+      <c r="A26" s="13"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -1901,7 +1935,7 @@
       <c r="A27" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="12" t="s">
         <v>65</v>
       </c>
       <c r="C27" s="2"/>
@@ -1966,7 +2000,7 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
+      <c r="A30" s="13"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1979,7 +2013,7 @@
       <c r="A31" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C31" s="2"/>
@@ -2219,7 +2253,7 @@
       <c r="A41" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="12" t="s">
         <v>76</v>
       </c>
       <c r="C41" s="2"/>
@@ -2308,6 +2342,26 @@
         <v>58</v>
       </c>
     </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+    </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>37</v>
@@ -2315,19 +2369,29 @@
       <c r="B48" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
+      <c r="C48" s="2">
+        <v>2</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="6">
+        <v>1350</v>
+      </c>
+      <c r="F48" s="6">
+        <v>1350</v>
+      </c>
       <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
+      <c r="H48" s="2" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>37</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -2341,31 +2405,134 @@
         <v>37</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="C50" s="2">
+        <v>6</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E50" s="6">
+        <v>497.7</v>
+      </c>
+      <c r="F50" s="6">
+        <f>C50*E50</f>
+        <v>2986.2</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
+      <c r="B51" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E51" s="6">
+        <v>299</v>
+      </c>
+      <c r="F51" s="6">
+        <f>C51*E51</f>
+        <v>299</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="2">
+        <v>10</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="6">
+        <v>28.35</v>
+      </c>
+      <c r="F52" s="6">
+        <f>C52*E52</f>
+        <v>283.5</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" s="2">
+        <v>4</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="6">
+        <v>29.25</v>
+      </c>
+      <c r="F53" s="6">
+        <f>C53*E53</f>
+        <v>117</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>42</v>
+      </c>
+      <c r="C54" s="2">
+        <v>20</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E54" s="6">
+        <v>29.61</v>
+      </c>
+      <c r="F54" s="6">
+        <f>C54*E54</f>
+        <v>592.20000000000005</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2399,9 +2566,14 @@
     <hyperlink ref="G33" r:id="rId27" xr:uid="{6E92EC5D-CAC7-440C-BF15-9DA01ECB766F}"/>
     <hyperlink ref="G36" r:id="rId28" xr:uid="{8249F3D4-5A22-4913-B3CE-0088DB84F686}"/>
     <hyperlink ref="G39" r:id="rId29" xr:uid="{18655CD5-F404-4A1C-BCC9-5252BAFDF36C}"/>
+    <hyperlink ref="G53" r:id="rId30" xr:uid="{303BBEF4-A747-4428-8609-08F72A9AA57A}"/>
+    <hyperlink ref="G50" r:id="rId31" xr:uid="{919B397D-E706-41C1-8F46-A4E5C53DB568}"/>
+    <hyperlink ref="G54" r:id="rId32" xr:uid="{185DD66E-4399-4E25-94B8-693B37381812}"/>
+    <hyperlink ref="G51" r:id="rId33" xr:uid="{1DE05233-E156-4AD3-AB51-F483E7BEB7AE}"/>
+    <hyperlink ref="G52" r:id="rId34" xr:uid="{5233D602-08FC-41DE-84BE-B1A5D23660A0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId30"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId35"/>
 </worksheet>
 </file>
 
@@ -2482,7 +2654,7 @@
       <c r="A4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C4" s="2"/>
@@ -2553,8 +2725,6 @@
       <c r="H6" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
@@ -2584,7 +2754,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -2592,14 +2762,12 @@
       <c r="F8" s="6"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C9" s="2"/>
@@ -2608,8 +2776,6 @@
       <c r="F9" s="6"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
@@ -2693,7 +2859,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="13"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -2706,7 +2872,7 @@
       <c r="A14" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="12" t="s">
         <v>65</v>
       </c>
       <c r="C14" s="2"/>
@@ -2771,7 +2937,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="13"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -2784,7 +2950,7 @@
       <c r="A18" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C18" s="2"/>
@@ -3024,7 +3190,7 @@
       <c r="A28" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="12" t="s">
         <v>76</v>
       </c>
       <c r="C28" s="2"/>
@@ -3138,6 +3304,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="38ca45d6-8f85-4c3a-993a-743aa40b1336" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010053414DE94637BA41B16756DFE4B8D2B8" ma:contentTypeVersion="16" ma:contentTypeDescription="Opret et nyt dokument." ma:contentTypeScope="" ma:versionID="49fd2ca43565d8a844063a34d6114918">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="38ca45d6-8f85-4c3a-993a-743aa40b1336" xmlns:ns4="b3a9d7bc-3d6e-49e0-996a-e43c1f0bf7ab" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1ff96052aa9fc0ac141bf2e3bdbf6a21" ns3:_="" ns4:_="">
     <xsd:import namespace="38ca45d6-8f85-4c3a-993a-743aa40b1336"/>
@@ -3376,14 +3550,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="38ca45d6-8f85-4c3a-993a-743aa40b1336" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3394,6 +3560,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E323FC16-0305-4970-AE77-B1379828493F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="b3a9d7bc-3d6e-49e0-996a-e43c1f0bf7ab"/>
+    <ds:schemaRef ds:uri="38ca45d6-8f85-4c3a-993a-743aa40b1336"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C28F24E-EFE3-4726-B043-086F7EA51039}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3412,23 +3595,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E323FC16-0305-4970-AE77-B1379828493F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="b3a9d7bc-3d6e-49e0-996a-e43c1f0bf7ab"/>
-    <ds:schemaRef ds:uri="38ca45d6-8f85-4c3a-993a-743aa40b1336"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1551DD82-85F6-480E-8CF8-03738D4C4012}">
   <ds:schemaRefs>

--- a/docs/v3/materialeliste.xlsx
+++ b/docs/v3/materialeliste.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742AF6E6-A45B-4CBE-BC3D-46955AB120BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15660" yWindow="0" windowWidth="33960" windowHeight="20985" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
+    <workbookView xWindow="3495" yWindow="810" windowWidth="34095" windowHeight="18300" xr2:uid="{5334E723-DA25-4B94-9819-AB5A8FEA0E43}"/>
   </bookViews>
   <sheets>
     <sheet name="materialeliste" sheetId="1" r:id="rId1"/>
@@ -3304,14 +3304,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="38ca45d6-8f85-4c3a-993a-743aa40b1336" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010053414DE94637BA41B16756DFE4B8D2B8" ma:contentTypeVersion="16" ma:contentTypeDescription="Opret et nyt dokument." ma:contentTypeScope="" ma:versionID="49fd2ca43565d8a844063a34d6114918">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="38ca45d6-8f85-4c3a-993a-743aa40b1336" xmlns:ns4="b3a9d7bc-3d6e-49e0-996a-e43c1f0bf7ab" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1ff96052aa9fc0ac141bf2e3bdbf6a21" ns3:_="" ns4:_="">
     <xsd:import namespace="38ca45d6-8f85-4c3a-993a-743aa40b1336"/>
@@ -3550,6 +3542,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="38ca45d6-8f85-4c3a-993a-743aa40b1336" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3560,23 +3560,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E323FC16-0305-4970-AE77-B1379828493F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="b3a9d7bc-3d6e-49e0-996a-e43c1f0bf7ab"/>
-    <ds:schemaRef ds:uri="38ca45d6-8f85-4c3a-993a-743aa40b1336"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C28F24E-EFE3-4726-B043-086F7EA51039}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3595,6 +3578,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E323FC16-0305-4970-AE77-B1379828493F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="b3a9d7bc-3d6e-49e0-996a-e43c1f0bf7ab"/>
+    <ds:schemaRef ds:uri="38ca45d6-8f85-4c3a-993a-743aa40b1336"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1551DD82-85F6-480E-8CF8-03738D4C4012}">
   <ds:schemaRefs>
